--- a/文件/專題甘特圖.xlsx
+++ b/文件/專題甘特圖.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/36338b096113435e/桌面/專題/goodbye/文件/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lzn\Desktop\Fork\goodbyeNewPro\文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_B9A090907DE409F734A0BDB5D22528E350C2CCE9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A18098AD-2E5C-4EA5-99D2-620C70265254}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9138BC47-12D5-4D1F-9EE1-FE200F3595B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>時間</t>
   </si>
@@ -94,14 +99,22 @@
     <t>內容
 上為預期進度
 下為實際進度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實際進度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>預期進度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -113,10 +126,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -146,8 +155,22 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,12 +201,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -358,71 +375,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -648,112 +682,112 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="29"/>
+      <c r="D1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="29"/>
+      <c r="L1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="29"/>
+      <c r="N1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="6" t="s">
+      <c r="O1" s="29"/>
+      <c r="P1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="6" t="s">
+      <c r="Q1" s="29"/>
+      <c r="R1" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="7"/>
-      <c r="T1" s="6" t="s">
+      <c r="S1" s="29"/>
+      <c r="T1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="7"/>
-      <c r="V1" s="6" t="s">
+      <c r="U1" s="29"/>
+      <c r="V1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="W1" s="7"/>
-      <c r="X1" s="6" t="s">
+      <c r="W1" s="29"/>
+      <c r="X1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="14" t="s">
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14" t="s">
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="AC1" s="18"/>
+      <c r="AC1" s="38"/>
     </row>
     <row r="2" spans="1:29" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="18"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="39"/>
     </row>
     <row r="3" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -776,15 +810,15 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="21"/>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="22"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="12"/>
     </row>
     <row r="4" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -807,38 +841,38 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="20"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="10"/>
     </row>
     <row r="5" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
       <c r="N5" s="5"/>
-      <c r="W5" s="12"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="21"/>
-      <c r="AB5" s="21"/>
-      <c r="AC5" s="22"/>
+      <c r="W5" s="6"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="12"/>
     </row>
     <row r="6" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -855,39 +889,39 @@
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="20"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="10"/>
     </row>
     <row r="7" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
       <c r="N7" s="5"/>
-      <c r="W7" s="12"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="22"/>
+      <c r="W7" s="6"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="12"/>
     </row>
     <row r="8" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="4"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -902,40 +936,40 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
       <c r="Y8" s="2"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
-      <c r="AC8" s="20"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="10"/>
     </row>
     <row r="9" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="32" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
       <c r="N9" s="5"/>
-      <c r="W9" s="12"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="21"/>
-      <c r="AA9" s="21"/>
-      <c r="AB9" s="21"/>
-      <c r="AC9" s="22"/>
+      <c r="W9" s="6"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="12"/>
     </row>
     <row r="10" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -950,30 +984,30 @@
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
       <c r="Y10" s="2"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-      <c r="AC10" s="20"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="10"/>
     </row>
     <row r="11" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
       <c r="N11" s="5"/>
-      <c r="W11" s="12"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="22"/>
+      <c r="W11" s="6"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="12"/>
     </row>
     <row r="12" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -981,53 +1015,52 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="13"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="W12" s="7"/>
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="20"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="10"/>
     </row>
     <row r="13" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="12"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="22"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="12"/>
     </row>
     <row r="14" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1037,51 +1070,51 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="32"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
       <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="20"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="10"/>
     </row>
     <row r="15" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="12"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="22"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="6"/>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="12"/>
     </row>
     <row r="16" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="4"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1089,46 +1122,46 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="20"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="10"/>
     </row>
     <row r="17" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="32" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="12"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="27"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="6"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="17"/>
     </row>
     <row r="18" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
+      <c r="A18" s="33"/>
       <c r="B18" s="4"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1137,11 +1170,11 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
       <c r="L18" s="2"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
@@ -1150,32 +1183,32 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
-      <c r="W18" s="32"/>
+      <c r="W18" s="22"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="20"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="10"/>
     </row>
     <row r="19" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="32" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="22"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="12"/>
     </row>
     <row r="20" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="4"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1188,7 +1221,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="30"/>
+      <c r="N20" s="20"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
@@ -1197,31 +1230,31 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
-      <c r="W20" s="32"/>
+      <c r="W20" s="22"/>
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="20"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="10"/>
     </row>
     <row r="21" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="32" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="3"/>
-      <c r="N21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="28"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="27"/>
+      <c r="N21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="18"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="17"/>
     </row>
     <row r="22" spans="1:29" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+      <c r="A22" s="33"/>
       <c r="B22" s="4"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1240,16 +1273,29 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
       <c r="X22" s="2"/>
       <c r="Y22" s="2"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="20"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="10"/>
+    </row>
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="13"/>
+    </row>
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="D25" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -1263,7 +1309,6 @@
     <mergeCell ref="V1:W2"/>
     <mergeCell ref="L1:M2"/>
     <mergeCell ref="N1:O2"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A3:A4"/>
@@ -1277,8 +1322,10 @@
     <mergeCell ref="D1:E2"/>
     <mergeCell ref="F1:G2"/>
     <mergeCell ref="H1:I2"/>
+    <mergeCell ref="A17:A18"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>